--- a/documentation/workflow/contracts_bronze_workflow_mapping.xlsx
+++ b/documentation/workflow/contracts_bronze_workflow_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fantasysuperkick/workspace/ccg/datawarehouse/documentation/workflow/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E13CFB-759F-544A-B32F-0166DD8DAA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B2EEAE-B9EA-4C46-AD5C-99940411CDB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="700" yWindow="500" windowWidth="28100" windowHeight="17500" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
+    <workbookView xWindow="700" yWindow="600" windowWidth="28100" windowHeight="17400" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
   </bookViews>
   <sheets>
     <sheet name="Historical" sheetId="2" r:id="rId1"/>
@@ -36,44 +36,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="74">
-  <si>
-    <t>PaymentTerms</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>SalespersonPurchaser</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="49">
   <si>
     <t>Location</t>
   </si>
   <si>
-    <t>GLAccount</t>
-  </si>
-  <si>
-    <t>GLEntry</t>
-  </si>
-  <si>
     <t>Customer</t>
   </si>
   <si>
-    <t>CustLedgerEntry</t>
-  </si>
-  <si>
-    <t>Vendor</t>
-  </si>
-  <si>
-    <t>VendorLedgerEntry</t>
-  </si>
-  <si>
     <t>Item</t>
   </si>
   <si>
-    <t>ItemLedgerEntry</t>
-  </si>
-  <si>
     <t>SalesHeader</t>
   </si>
   <si>
@@ -98,9 +71,6 @@
     <t>PurchInvLine</t>
   </si>
   <si>
-    <t>entryno</t>
-  </si>
-  <si>
     <t>no</t>
   </si>
   <si>
@@ -110,9 +80,6 @@
     <t>code, name</t>
   </si>
   <si>
-    <t>code, description</t>
-  </si>
-  <si>
     <t>phoneno, address, mobilephoneno</t>
   </si>
   <si>
@@ -125,9 +92,6 @@
     <t>Prescriber</t>
   </si>
   <si>
-    <t>Facility</t>
-  </si>
-  <si>
     <t>contactno, city, postcode, county, countryregioncode</t>
   </si>
   <si>
@@ -149,34 +113,10 @@
     <t>Bronze_Deduplication_Keys</t>
   </si>
   <si>
-    <t>jobtitle</t>
-  </si>
-  <si>
     <t>postcode, county, countryregioncode</t>
   </si>
   <si>
-    <t>no, name</t>
-  </si>
-  <si>
-    <t>accounttype, globaldimension1code, globaldimension2code, accountcategory</t>
-  </si>
-  <si>
-    <t>glaccountno,documenttype, globaldimension1code, globaldimension2code, sourcecode,sourcetype</t>
-  </si>
-  <si>
-    <t>customerno, documenttype, selltocustomerno, customerpostinggroup, globaldimension1code, globaldimension2code, salespersoncode, sourcecode,  balaccounttype, balaccountno</t>
-  </si>
-  <si>
-    <t>city, postcode, globaldimension1code, globaldimension2code, vendorpostinggroup, currencycode, languagecode, paymenttermscode, purchasercode, shipmentmethodcode, shippingagentcode,  paytovendorno, paymentmethodcode, countryregioncode</t>
-  </si>
-  <si>
-    <t>documenttype, vendorno,  buyfromvendorno, globaldimension1code, globaldimension2code, purchasercode, sourcecode, balaccounttype</t>
-  </si>
-  <si>
     <t>originating_company</t>
-  </si>
-  <si>
-    <t>itemno, entrytype, sourceno, locationcode,  globaldimension1code, globaldimension2code,  shptmethodcode, sourcetype, itemtracking, packageno</t>
   </si>
   <si>
     <t>documenttype, selltocustomerno, no,  type,  locationcode, postinggroup, unitofmeasure,  shortcutdimension1code, shortcutdimension2code, customerpricegroup,  billtocustomerno,  purchaseorderno,  genbuspostinggroup,  genprodpostinggroup, vatcalculationtype,  transactiontype,  transportmethod,  taxcategory, vatbuspostinggroup, vatprodpostinggroup, currencycode, vatidentifier, prepmtvatcalctype, dimensionsetid, bincode, unitofmeasure,  itemcategorycode,  shippingagentcode,  shippingagentservicecode</t>
@@ -288,39 +228,15 @@
     </r>
   </si>
   <si>
-    <t>entryno,originating_company,source_system</t>
-  </si>
-  <si>
-    <t>entryno,itemno,originating_company,source_system</t>
-  </si>
-  <si>
     <t>documentno, lineno,originating_company, source_system</t>
   </si>
   <si>
     <t>no, originating_company,source_system</t>
   </si>
   <si>
-    <t>no, name, originating_company, source_system</t>
-  </si>
-  <si>
     <t>code, name, originating_company, source_system</t>
   </si>
   <si>
-    <t>code, description, originating_company, source_system</t>
-  </si>
-  <si>
-    <t>entryno, originating_company</t>
-  </si>
-  <si>
-    <t>entryno,originating_company</t>
-  </si>
-  <si>
-    <t>entryno, vendorno, originating_company</t>
-  </si>
-  <si>
-    <t>entryno, itemno,originating_originating_company</t>
-  </si>
-  <si>
     <t>no, originating_company</t>
   </si>
   <si>
@@ -334,6 +250,15 @@
   </si>
   <si>
     <t>city, postcode, globaldimension1code, globaldimension2code, customerpostinggroup, customerpricegroup, languagecode, paymenttermscode, salespersoncode, shipmentmethodcode, shippingagentcode,  customerdiscgroup, countryregioncode,  billtocustomerno, locationcode, contacttype</t>
+  </si>
+  <si>
+    <t>ItemVariant</t>
+  </si>
+  <si>
+    <t>code, description, company, source_system</t>
+  </si>
+  <si>
+    <t>itemno</t>
   </si>
 </sst>
 </file>
@@ -778,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBA92A4A-7349-FF40-A839-841302118E9B}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
@@ -791,476 +716,299 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>47</v>
+      </c>
+      <c r="E2" t="s">
+        <v>48</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>37</v>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>45</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>45</v>
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>73</v>
+      <c r="E8" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="E12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" t="s">
-        <v>69</v>
-      </c>
-      <c r="E12" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" t="s">
-        <v>46</v>
+        <v>42</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="F13" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" t="s">
-        <v>49</v>
-      </c>
-      <c r="F18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" t="s">
-        <v>70</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F21" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" t="s">
-        <v>30</v>
-      </c>
-      <c r="F23" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" t="s">
-        <v>56</v>
-      </c>
-      <c r="E24" t="s">
-        <v>30</v>
-      </c>
-      <c r="F24" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/documentation/workflow/contracts_bronze_workflow_mapping.xlsx
+++ b/documentation/workflow/contracts_bronze_workflow_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fantasysuperkick/workspace/ccg/datawarehouse/documentation/workflow/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B2EEAE-B9EA-4C46-AD5C-99940411CDB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D172361-E3AA-B242-9989-EA3108DE4528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="700" yWindow="600" windowWidth="28100" windowHeight="17400" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
+    <workbookView xWindow="780" yWindow="600" windowWidth="28020" windowHeight="17400" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
   </bookViews>
   <sheets>
     <sheet name="Historical" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="51">
   <si>
     <t>Location</t>
   </si>
@@ -90,9 +90,6 @@
   </si>
   <si>
     <t>Prescriber</t>
-  </si>
-  <si>
-    <t>contactno, city, postcode, county, countryregioncode</t>
   </si>
   <si>
     <t xml:space="preserve">documenttype, buyfromvendorno,no , type, locationcode, postinggroup, paytovendorno, genbuspostinggroup, genprodpostinggroup,  vatcalculationtype, transactiontype, transportmethod, vatbuspostinggroup, vatprodpostinggroup, currencycode,  vatidentifier,  fapostingtype,  depreciationbookcode,  maintenancecode,  insuranceno,  budgetedfano,  responsibilitycenter, itemcategorycode </t>
@@ -184,9 +181,6 @@
     <t>FundingBody</t>
   </si>
   <si>
-    <t>phoneno, address</t>
-  </si>
-  <si>
     <r>
       <t>selltocustomerno,</t>
     </r>
@@ -228,9 +222,6 @@
     </r>
   </si>
   <si>
-    <t>documentno, lineno,originating_company, source_system</t>
-  </si>
-  <si>
     <t>no, originating_company,source_system</t>
   </si>
   <si>
@@ -240,15 +231,6 @@
     <t>no, originating_company</t>
   </si>
   <si>
-    <t>documentno, lineno, originating_company</t>
-  </si>
-  <si>
-    <t>no,originating_company</t>
-  </si>
-  <si>
-    <t>no,originating_company,source_system</t>
-  </si>
-  <si>
     <t>city, postcode, globaldimension1code, globaldimension2code, customerpostinggroup, customerpricegroup, languagecode, paymenttermscode, salespersoncode, shipmentmethodcode, shippingagentcode,  customerdiscgroup, countryregioncode,  billtocustomerno, locationcode, contacttype</t>
   </si>
   <si>
@@ -259,6 +241,30 @@
   </si>
   <si>
     <t>itemno</t>
+  </si>
+  <si>
+    <t>no, company</t>
+  </si>
+  <si>
+    <t>documentno, lineno, company</t>
+  </si>
+  <si>
+    <t>no,company</t>
+  </si>
+  <si>
+    <t>no, company,source_system</t>
+  </si>
+  <si>
+    <t>documentno, lineno,company, source_system</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> postcode, state</t>
+  </si>
+  <si>
+    <t>phoneno</t>
+  </si>
+  <si>
+    <t>no,company,source_system</t>
   </si>
 </sst>
 </file>
@@ -719,36 +725,36 @@
         <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -759,16 +765,16 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -779,16 +785,16 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -799,16 +805,16 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -819,16 +825,16 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -836,19 +842,19 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -859,16 +865,16 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -876,19 +882,19 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -899,16 +905,16 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="18" x14ac:dyDescent="0.2">
@@ -916,19 +922,19 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="18" x14ac:dyDescent="0.2">
@@ -939,16 +945,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="18" x14ac:dyDescent="0.2">
@@ -956,19 +962,19 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -979,36 +985,33 @@
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="F14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/documentation/workflow/contracts_bronze_workflow_mapping.xlsx
+++ b/documentation/workflow/contracts_bronze_workflow_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fantasysuperkick/workspace/ccg/datawarehouse/documentation/workflow/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D172361-E3AA-B242-9989-EA3108DE4528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B221A4-2FC3-714F-B0F9-EFBA1ECB2F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="600" windowWidth="28020" windowHeight="17400" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
   </bookViews>
@@ -237,9 +237,6 @@
     <t>ItemVariant</t>
   </si>
   <si>
-    <t>code, description, company, source_system</t>
-  </si>
-  <si>
     <t>itemno</t>
   </si>
   <si>
@@ -265,6 +262,9 @@
   </si>
   <si>
     <t>no,company,source_system</t>
+  </si>
+  <si>
+    <t>code, description, originating_company, source_system</t>
   </si>
 </sst>
 </file>
@@ -745,13 +745,13 @@
         <v>40</v>
       </c>
       <c r="C2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" t="s">
         <v>41</v>
-      </c>
-      <c r="D2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" t="s">
-        <v>42</v>
       </c>
       <c r="F2" t="s">
         <v>25</v>
@@ -785,7 +785,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
@@ -825,10 +825,10 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
         <v>32</v>
@@ -845,10 +845,10 @@
         <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
         <v>26</v>
@@ -865,7 +865,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>38</v>
@@ -885,10 +885,10 @@
         <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
         <v>18</v>
@@ -905,10 +905,10 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
@@ -925,10 +925,10 @@
         <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>35</v>
@@ -945,10 +945,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>29</v>
@@ -965,10 +965,10 @@
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>30</v>
@@ -991,7 +991,7 @@
         <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F14" t="s">
         <v>25</v>
@@ -1008,7 +1008,7 @@
         <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F15" t="s">
         <v>25</v>

--- a/documentation/workflow/contracts_bronze_workflow_mapping.xlsx
+++ b/documentation/workflow/contracts_bronze_workflow_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fantasysuperkick/workspace/ccg/datawarehouse/documentation/workflow/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B221A4-2FC3-714F-B0F9-EFBA1ECB2F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A24531-E569-2343-B259-986755401E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="600" windowWidth="28020" windowHeight="17400" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
   </bookViews>
@@ -1005,7 +1005,7 @@
         <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
         <v>48</v>
